--- a/artfynd/A 43541-2022 artfynd.xlsx
+++ b/artfynd/A 43541-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129412731</v>
       </c>
       <c r="B3" t="n">
-        <v>100436</v>
+        <v>100714</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43541-2022 artfynd.xlsx
+++ b/artfynd/A 43541-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129412731</v>
       </c>
       <c r="B3" t="n">
-        <v>100714</v>
+        <v>100724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43541-2022 artfynd.xlsx
+++ b/artfynd/A 43541-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129412731</v>
       </c>
       <c r="B3" t="n">
-        <v>100724</v>
+        <v>100725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43541-2022 artfynd.xlsx
+++ b/artfynd/A 43541-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129412731</v>
       </c>
       <c r="B3" t="n">
-        <v>100725</v>
+        <v>100730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43541-2022 artfynd.xlsx
+++ b/artfynd/A 43541-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129412731</v>
       </c>
       <c r="B3" t="n">
-        <v>100730</v>
+        <v>100733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43541-2022 artfynd.xlsx
+++ b/artfynd/A 43541-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129412731</v>
       </c>
       <c r="B3" t="n">
-        <v>100733</v>
+        <v>100739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43541-2022 artfynd.xlsx
+++ b/artfynd/A 43541-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129412731</v>
       </c>
       <c r="B3" t="n">
-        <v>100739</v>
+        <v>100751</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43541-2022 artfynd.xlsx
+++ b/artfynd/A 43541-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129412731</v>
       </c>
       <c r="B3" t="n">
-        <v>100751</v>
+        <v>100752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43541-2022 artfynd.xlsx
+++ b/artfynd/A 43541-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129412731</v>
       </c>
       <c r="B3" t="n">
-        <v>100752</v>
+        <v>100755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43541-2022 artfynd.xlsx
+++ b/artfynd/A 43541-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129412731</v>
       </c>
       <c r="B3" t="n">
-        <v>100755</v>
+        <v>100759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
